--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/DELAWARE_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/DELAWARE_2014.xlsx
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C121">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C273">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C448">
